--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_buff.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_buff.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="793">
   <si>
     <t>buff序号</t>
   </si>
@@ -5712,13 +5712,7 @@
     <t>弓箭手治疗瞬间回复</t>
   </si>
   <si>
-    <t>207031#1|207031#1</t>
-  </si>
-  <si>
-    <t>6#7</t>
-  </si>
-  <si>
-    <t>207031#5|10003#2000</t>
+    <t>10003#20000</t>
   </si>
   <si>
     <t>战神之力</t>
@@ -15317,13 +15311,13 @@
         <v>3</v>
       </c>
       <c r="F168" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G168" s="2">
+        <v>7</v>
+      </c>
+      <c r="H168" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="G168" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="H168" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="I168" s="2">
         <v>3</v>
@@ -15346,10 +15340,10 @@
         <v>130000302</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E171" s="3">
         <v>3</v>
@@ -15361,7 +15355,7 @@
         <v>6</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="I171" s="3">
         <v>3</v>
@@ -15379,10 +15373,10 @@
         <v>1</v>
       </c>
       <c r="AE171" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF171" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AH171" s="3">
         <v>1</v>
@@ -15393,10 +15387,10 @@
         <v>130000303</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E172" s="3">
         <v>3</v>
@@ -15408,7 +15402,7 @@
         <v>6</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I172" s="3">
         <v>3</v>
@@ -15426,10 +15420,10 @@
         <v>1</v>
       </c>
       <c r="AE172" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF172" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AH172" s="3">
         <v>1</v>
@@ -15440,10 +15434,10 @@
         <v>130000304</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E173" s="3">
         <v>3</v>
@@ -15455,7 +15449,7 @@
         <v>6</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="I173" s="3">
         <v>3</v>
@@ -15473,10 +15467,10 @@
         <v>1</v>
       </c>
       <c r="AE173" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF173" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AH173" s="3">
         <v>1</v>
@@ -15487,10 +15481,10 @@
         <v>130000305</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E174" s="3">
         <v>3</v>
@@ -15502,7 +15496,7 @@
         <v>6</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="I174" s="3">
         <v>3</v>
@@ -15520,10 +15514,10 @@
         <v>1</v>
       </c>
       <c r="AE174" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF174" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AH174" s="3">
         <v>1</v>
@@ -15534,10 +15528,10 @@
         <v>130000101</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E175" s="3">
         <v>3</v>
@@ -15570,10 +15564,10 @@
         <v>130000102</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E176" s="3">
         <v>3</v>
@@ -15605,10 +15599,10 @@
         <v>130000601</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E177" s="3">
         <v>3</v>
@@ -15641,10 +15635,10 @@
         <v>130000602</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E178" s="3">
         <v>3</v>
@@ -15676,10 +15670,10 @@
         <v>130000603</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E179" s="3">
         <v>2</v>
@@ -15715,10 +15709,10 @@
         <v>3</v>
       </c>
       <c r="AE179" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AF179" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AH179" s="3">
         <v>1</v>
@@ -15729,10 +15723,10 @@
         <v>130000201</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E180" s="3">
         <v>3</v>
@@ -15765,10 +15759,10 @@
         <v>130000202</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E181" s="3">
         <v>3</v>
@@ -15801,10 +15795,10 @@
         <v>130000402</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E183" s="3">
         <v>3</v>
@@ -15837,10 +15831,10 @@
         <v>32</v>
       </c>
       <c r="AE183" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="AF183" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="AF183" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="AH183" s="3">
         <v>1</v>
@@ -15851,10 +15845,10 @@
         <v>130000403</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E184" s="3">
         <v>3</v>
@@ -15884,10 +15878,10 @@
         <v>32</v>
       </c>
       <c r="AE184" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AF184" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AH184" s="3">
         <v>1</v>
@@ -15898,10 +15892,10 @@
         <v>130000404</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E185" s="3">
         <v>3</v>
@@ -15928,10 +15922,10 @@
         <v>32</v>
       </c>
       <c r="AE185" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AF185" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AH185" s="3">
         <v>1</v>
@@ -15942,10 +15936,10 @@
         <v>130000405</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E186" s="3">
         <v>3</v>
@@ -15972,10 +15966,10 @@
         <v>32</v>
       </c>
       <c r="AE186" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AF186" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AH186" s="3">
         <v>1</v>
@@ -15986,10 +15980,10 @@
         <v>102006401</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E187" s="3">
         <v>3</v>
@@ -16001,7 +15995,7 @@
         <v>7</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I187" s="3">
         <v>4</v>
@@ -16022,10 +16016,10 @@
         <v>102006501</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E188" s="3">
         <v>3</v>
@@ -16037,7 +16031,7 @@
         <v>7</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="I188" s="3">
         <v>4</v>
@@ -16058,22 +16052,22 @@
         <v>200003101</v>
       </c>
       <c r="B189" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="E189" s="3">
+        <v>3</v>
+      </c>
+      <c r="F189" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="E189" s="3">
-        <v>3</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>500</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I189" s="3">
         <v>4</v>
@@ -16096,10 +16090,10 @@
         <v>200004101</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E190" s="3">
         <v>3</v>
@@ -16129,10 +16123,10 @@
         <v>15</v>
       </c>
       <c r="AE190" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="AF190" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="AF190" s="4" t="s">
-        <v>630</v>
       </c>
       <c r="AI190" s="3">
         <v>1</v>
@@ -16143,10 +16137,10 @@
         <v>200006101</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E191" s="3">
         <v>2</v>
@@ -16155,7 +16149,7 @@
         <v>29</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="I191" s="3">
         <v>4</v>
@@ -16173,10 +16167,10 @@
         <v>4</v>
       </c>
       <c r="AE191" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AF191" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AI191" s="3">
         <v>1</v>
@@ -16187,10 +16181,10 @@
         <v>200005201</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E192" s="3">
         <v>3</v>
@@ -16202,7 +16196,7 @@
         <v>7</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I192" s="3">
         <v>1</v>
@@ -16223,10 +16217,10 @@
         <v>46</v>
       </c>
       <c r="AE192" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AF192" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AI192" s="3">
         <v>1</v>
@@ -16237,22 +16231,22 @@
         <v>220002101</v>
       </c>
       <c r="B193" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="E193" s="3">
+        <v>3</v>
+      </c>
+      <c r="F193" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="E193" s="3">
-        <v>3</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>641</v>
       </c>
       <c r="G193" s="3">
         <v>6</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I193" s="3">
         <v>4</v>
@@ -16272,22 +16266,22 @@
         <v>220002102</v>
       </c>
       <c r="B194" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="E194" s="3">
+        <v>3</v>
+      </c>
+      <c r="F194" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="C194" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="E194" s="3">
-        <v>3</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>641</v>
       </c>
       <c r="G194" s="3">
         <v>6</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="I194" s="3">
         <v>4</v>
@@ -16307,22 +16301,22 @@
         <v>220003101</v>
       </c>
       <c r="B195" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E195" s="3">
+        <v>3</v>
+      </c>
+      <c r="F195" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E195" s="3">
-        <v>3</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>647</v>
       </c>
       <c r="G195" s="3">
         <v>6</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="I195" s="3">
         <v>4</v>
@@ -16342,22 +16336,22 @@
         <v>220003102</v>
       </c>
       <c r="B196" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="E196" s="3">
+        <v>3</v>
+      </c>
+      <c r="F196" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="E196" s="3">
-        <v>3</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>647</v>
       </c>
       <c r="G196" s="3">
         <v>6</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="I196" s="3">
         <v>4</v>
@@ -16377,10 +16371,10 @@
         <v>220003201</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E197" s="3">
         <v>3</v>
@@ -16392,7 +16386,7 @@
         <v>6</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="I197" s="3">
         <v>4</v>
@@ -16410,10 +16404,10 @@
         <v>19</v>
       </c>
       <c r="AE197" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AF197" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AI197" s="3">
         <v>1</v>
@@ -16424,22 +16418,22 @@
         <v>220004101</v>
       </c>
       <c r="B198" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E198" s="3">
+        <v>3</v>
+      </c>
+      <c r="F198" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="E198" s="3">
-        <v>3</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>657</v>
       </c>
       <c r="G198" s="3">
         <v>6</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="I198" s="3">
         <v>4</v>
@@ -16459,22 +16453,22 @@
         <v>220004102</v>
       </c>
       <c r="B199" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="E199" s="3">
+        <v>3</v>
+      </c>
+      <c r="F199" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="E199" s="3">
-        <v>3</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>657</v>
       </c>
       <c r="G199" s="3">
         <v>6</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="I199" s="3">
         <v>4</v>
@@ -16494,22 +16488,22 @@
         <v>220004201</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E200" s="3">
         <v>3</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G200" s="3">
         <v>6</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="I200" s="3">
         <v>1</v>
@@ -16527,10 +16521,10 @@
         <v>38</v>
       </c>
       <c r="AE200" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AF200" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AI200" s="3">
         <v>1</v>
@@ -16541,10 +16535,10 @@
         <v>220005101</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E201" s="3">
         <v>5</v>
@@ -16553,7 +16547,7 @@
         <v>1</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I201" s="3">
         <v>4</v>
@@ -16570,10 +16564,10 @@
         <v>220005102</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E202" s="3">
         <v>5</v>
@@ -16582,7 +16576,7 @@
         <v>1</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I202" s="3">
         <v>4</v>
@@ -16599,10 +16593,10 @@
         <v>220005201</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E203" s="3">
         <v>3</v>
@@ -16614,7 +16608,7 @@
         <v>6</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I203" s="3">
         <v>1</v>
@@ -16637,10 +16631,10 @@
         <v>220006101</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E204" s="3">
         <v>3</v>
@@ -16652,7 +16646,7 @@
         <v>7</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="I204" s="3">
         <v>4</v>
@@ -16678,10 +16672,10 @@
         <v>220006102</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E205" s="3">
         <v>3</v>
@@ -16693,7 +16687,7 @@
         <v>7</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="I205" s="3">
         <v>4</v>
@@ -16719,22 +16713,22 @@
         <v>220006201</v>
       </c>
       <c r="B206" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E206" s="3">
+        <v>3</v>
+      </c>
+      <c r="F206" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="E206" s="3">
-        <v>3</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>678</v>
       </c>
       <c r="G206" s="3">
         <v>6</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I206" s="3">
         <v>4</v>
@@ -16757,10 +16751,10 @@
         <v>230000001</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E207" s="3">
         <v>3</v>
@@ -16772,7 +16766,7 @@
         <v>7</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I207" s="3">
         <v>1</v>
@@ -16789,22 +16783,22 @@
         <v>100402301</v>
       </c>
       <c r="B208" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="E208" s="3">
+        <v>3</v>
+      </c>
+      <c r="F208" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="E208" s="3">
-        <v>3</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>500</v>
       </c>
       <c r="H208" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="I208" s="3">
         <v>4</v>
@@ -16825,7 +16819,7 @@
         <v>38</v>
       </c>
       <c r="AE208" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AF208" s="3">
         <v>1111</v>
@@ -16836,10 +16830,10 @@
         <v>100402302</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E209" s="3">
         <v>5</v>
@@ -16848,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="I209" s="3">
         <v>4</v>
@@ -16869,7 +16863,7 @@
         <v>38</v>
       </c>
       <c r="AE209" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AF209" s="3">
         <v>1111</v>
@@ -16880,10 +16874,10 @@
         <v>101601601</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E210" s="3">
         <v>3</v>
@@ -16915,10 +16909,10 @@
         <v>100500201</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E211" s="3">
         <v>2</v>
@@ -16938,10 +16932,10 @@
         <v>100500202</v>
       </c>
       <c r="B212" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>688</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>690</v>
       </c>
       <c r="E212" s="3">
         <v>2</v>
@@ -16968,7 +16962,7 @@
         <v>454</v>
       </c>
       <c r="C213" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E213" s="2">
         <v>3</v>
@@ -16980,7 +16974,7 @@
         <v>11</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="I213" s="2">
         <v>3</v>
@@ -17004,7 +16998,7 @@
         <v>454</v>
       </c>
       <c r="AF213" s="10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AH213" s="2">
         <v>1</v>
@@ -17015,10 +17009,10 @@
         <v>110000708</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C214" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E214" s="2">
         <v>3</v>
@@ -17030,7 +17024,7 @@
         <v>11</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I214" s="2">
         <v>4</v>
@@ -17054,7 +17048,7 @@
         <v>454</v>
       </c>
       <c r="AF214" s="10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AH214" s="2">
         <v>1</v>
@@ -17071,19 +17065,19 @@
         <v>512</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E215" s="2">
         <v>3</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G215" s="2">
         <v>11</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I215" s="2">
         <v>3</v>
@@ -17107,7 +17101,7 @@
         <v>512</v>
       </c>
       <c r="AF215" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AH215" s="2">
         <v>1</v>
@@ -17118,22 +17112,22 @@
         <v>120001108</v>
       </c>
       <c r="B216" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E216" s="2">
         <v>3</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G216" s="2">
         <v>11</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I216" s="2">
         <v>4</v>
@@ -17157,7 +17151,7 @@
         <v>512</v>
       </c>
       <c r="AF216" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AH216" s="2">
         <v>1</v>
@@ -17171,10 +17165,10 @@
         <v>130000401</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E217" s="3">
         <v>3</v>
@@ -17186,7 +17180,7 @@
         <v>11</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I217" s="3">
         <v>3</v>
@@ -17207,10 +17201,10 @@
         <v>32</v>
       </c>
       <c r="AE217" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AF217" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AH217" s="3">
         <v>1</v>
@@ -17221,10 +17215,10 @@
         <v>130000408</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C218" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E218" s="3">
         <v>3</v>
@@ -17236,7 +17230,7 @@
         <v>11</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I218" s="3">
         <v>4</v>
@@ -17257,10 +17251,10 @@
         <v>32</v>
       </c>
       <c r="AE218" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AF218" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AH218" s="3">
         <v>1</v>
@@ -17274,22 +17268,22 @@
         <v>130000301</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E219" s="3">
         <v>3</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G219" s="2">
         <v>11</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I219" s="3">
         <v>3</v>
@@ -17307,10 +17301,10 @@
         <v>1</v>
       </c>
       <c r="AE219" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF219" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AH219" s="3">
         <v>1</v>
@@ -17321,22 +17315,22 @@
         <v>130000308</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E220" s="2">
         <v>3</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G220" s="2">
         <v>11</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="I220" s="2">
         <v>4</v>
@@ -17354,10 +17348,10 @@
         <v>1</v>
       </c>
       <c r="AE220" s="10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AF220" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AH220" s="2">
         <v>1</v>
@@ -17371,10 +17365,10 @@
         <v>250001014</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E221" s="2">
         <v>3</v>
@@ -17404,10 +17398,10 @@
         <v>100500403</v>
       </c>
       <c r="B222" s="14" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E222" s="3">
         <v>2</v>
@@ -17436,10 +17430,10 @@
         <v>101</v>
       </c>
       <c r="AE222" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="AF222" s="4" t="s">
         <v>710</v>
-      </c>
-      <c r="AF222" s="4" t="s">
-        <v>712</v>
       </c>
       <c r="AG222" s="4"/>
       <c r="AH222" s="3"/>
@@ -17449,10 +17443,10 @@
         <v>100500406</v>
       </c>
       <c r="B223" s="14" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E223" s="3">
         <v>2</v>
@@ -17481,10 +17475,10 @@
         <v>103</v>
       </c>
       <c r="AE223" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="AF223" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="AG223" s="4"/>
       <c r="AH223" s="3"/>
@@ -17494,22 +17488,22 @@
         <v>240001003</v>
       </c>
       <c r="B224" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="C224" t="s">
+        <v>714</v>
+      </c>
+      <c r="E224" s="3">
+        <v>3</v>
+      </c>
+      <c r="F224" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="C224" t="s">
-        <v>716</v>
-      </c>
-      <c r="E224" s="3">
-        <v>3</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>717</v>
       </c>
       <c r="G224" s="3">
         <v>6</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="I224" s="3">
         <v>4</v>
@@ -17529,10 +17523,10 @@
         <v>32</v>
       </c>
       <c r="AE224" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="AF224" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="225" customFormat="1" spans="1:36">
@@ -17540,28 +17534,28 @@
         <v>250001009</v>
       </c>
       <c r="B225" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="C225" t="s">
+        <v>719</v>
+      </c>
+      <c r="E225" s="3">
+        <v>3</v>
+      </c>
+      <c r="F225" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="C225" t="s">
-        <v>721</v>
-      </c>
-      <c r="E225" s="3">
-        <v>3</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>722</v>
       </c>
       <c r="G225" s="3">
         <v>6</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="I225" s="3">
         <v>1</v>
       </c>
-      <c r="L225" s="3">
-        <v>15000</v>
+      <c r="L225" s="2">
+        <v>300000</v>
       </c>
       <c r="M225" s="3"/>
       <c r="N225" s="3">
@@ -17575,10 +17569,10 @@
         <v>33</v>
       </c>
       <c r="AE225" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AF225" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="226" customFormat="1" spans="1:36">
@@ -17586,28 +17580,28 @@
         <v>250001010</v>
       </c>
       <c r="B226" s="16" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C226" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E226" s="3">
         <v>3</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G226" s="3">
         <v>6</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="I226" s="3">
         <v>1</v>
       </c>
-      <c r="L226" s="3">
-        <v>15000</v>
+      <c r="L226" s="2">
+        <v>300000</v>
       </c>
       <c r="M226" s="3"/>
       <c r="N226" s="3">
@@ -17621,10 +17615,10 @@
         <v>33</v>
       </c>
       <c r="AE226" s="3" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AF226" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="227" ht="16.5" spans="1:36">
@@ -17632,22 +17626,22 @@
         <v>1300000401</v>
       </c>
       <c r="B227" s="17" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C227" s="17" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E227" s="3">
         <v>3</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>500</v>
       </c>
       <c r="H227" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="I227" s="3">
         <v>4</v>
@@ -17665,10 +17659,10 @@
         <v>3</v>
       </c>
       <c r="AE227" s="17" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AF227" s="18" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AH227" s="3">
         <v>1</v>
@@ -17682,10 +17676,10 @@
         <v>1300000402</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C228" s="17" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E228" s="3">
         <v>3</v>
@@ -17697,7 +17691,7 @@
         <v>6</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="I228" s="3">
         <v>4</v>
@@ -17715,10 +17709,10 @@
         <v>4</v>
       </c>
       <c r="AE228" s="17" t="s">
+        <v>731</v>
+      </c>
+      <c r="AF228" s="18" t="s">
         <v>733</v>
-      </c>
-      <c r="AF228" s="18" t="s">
-        <v>735</v>
       </c>
       <c r="AH228" s="3">
         <v>1</v>
@@ -17732,22 +17726,22 @@
         <v>1300000403</v>
       </c>
       <c r="B229" s="17" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C229" s="17" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E229" s="3">
         <v>3</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G229" s="3">
         <v>6</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="I229" s="3">
         <v>4</v>
@@ -17765,10 +17759,10 @@
         <v>1</v>
       </c>
       <c r="AE229" s="17" t="s">
+        <v>734</v>
+      </c>
+      <c r="AF229" s="18" t="s">
         <v>736</v>
-      </c>
-      <c r="AF229" s="18" t="s">
-        <v>738</v>
       </c>
       <c r="AH229" s="3">
         <v>1</v>
@@ -17782,22 +17776,22 @@
         <v>1300000404</v>
       </c>
       <c r="B230" s="17" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C230" s="17" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E230" s="3">
         <v>3</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G230" s="3">
         <v>6</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="I230" s="3">
         <v>4</v>
@@ -17815,10 +17809,10 @@
         <v>6</v>
       </c>
       <c r="AE230" s="17" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="AF230" s="18" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="AH230" s="3">
         <v>1</v>
@@ -17832,22 +17826,22 @@
         <v>1300000405</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C231" s="17" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E231" s="3">
         <v>3</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G231" s="3">
         <v>6</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="I231" s="3">
         <v>4</v>
@@ -17865,10 +17859,10 @@
         <v>8</v>
       </c>
       <c r="AE231" s="17" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AF231" s="18" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="AH231" s="3">
         <v>1</v>
@@ -17882,22 +17876,22 @@
         <v>1300000406</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C232" s="17" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E232" s="3">
         <v>3</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G232" s="3">
         <v>6</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="I232" s="3">
         <v>4</v>
@@ -17915,10 +17909,10 @@
         <v>42</v>
       </c>
       <c r="AE232" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="AF232" s="4" t="s">
         <v>747</v>
-      </c>
-      <c r="AF232" s="4" t="s">
-        <v>749</v>
       </c>
       <c r="AH232" s="3">
         <v>1</v>
@@ -17932,23 +17926,23 @@
         <v>10300002</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="3">
         <v>3</v>
       </c>
       <c r="F233" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="H233" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="H233" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="I233" s="3">
         <v>4</v>
@@ -18003,10 +17997,10 @@
         <v>53</v>
       </c>
       <c r="AE233" s="4" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="AF233" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AG233" s="3" t="s">
         <v>142</v>
@@ -18021,23 +18015,23 @@
         <v>10300003</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D234" s="3"/>
       <c r="E234" s="3">
         <v>3</v>
       </c>
       <c r="F234" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="H234" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="H234" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="I234" s="3">
         <v>4</v>
@@ -18092,10 +18086,10 @@
         <v>53</v>
       </c>
       <c r="AE234" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AF234" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AG234" s="3" t="s">
         <v>142</v>
@@ -18112,22 +18106,22 @@
         <v>1300000407</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C235" s="17" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E235" s="3">
         <v>3</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G235" s="3">
         <v>6</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="I235" s="3">
         <v>4</v>
@@ -18145,10 +18139,10 @@
         <v>44</v>
       </c>
       <c r="AE235" s="17" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AF235" s="4" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AH235" s="3">
         <v>1</v>
@@ -18162,22 +18156,22 @@
         <v>1300000408</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C236" s="17" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E236" s="3">
         <v>3</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G236" s="3">
         <v>6</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="I236" s="3">
         <v>4</v>
@@ -18195,10 +18189,10 @@
         <v>43</v>
       </c>
       <c r="AE236" s="17" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AF236" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AH236" s="3">
         <v>1</v>
@@ -18212,27 +18206,27 @@
         <v>250001007</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="E237" s="3">
+        <v>3</v>
+      </c>
+      <c r="F237" s="3" t="s">
         <v>767</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="E237" s="3">
-        <v>3</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>769</v>
       </c>
       <c r="G237" s="3">
         <v>6</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="I237" s="3">
         <v>4</v>
       </c>
-      <c r="L237" s="3">
+      <c r="L237" s="2">
         <v>300000</v>
       </c>
       <c r="N237" s="3">
@@ -18248,10 +18242,10 @@
         <v>117</v>
       </c>
       <c r="AE237" s="4" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AF237" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="238" customFormat="1" spans="1:36">
@@ -18259,22 +18253,22 @@
         <v>20000906</v>
       </c>
       <c r="B238" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E238" s="3">
+        <v>3</v>
+      </c>
+      <c r="F238" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="G238" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="E238" s="3">
-        <v>3</v>
-      </c>
-      <c r="F238" s="3" t="s">
+      <c r="H238" s="3" t="s">
         <v>774</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>776</v>
       </c>
       <c r="I238" s="3">
         <v>4</v>
@@ -18302,10 +18296,10 @@
         <v>144</v>
       </c>
       <c r="AE238" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AF238" s="4" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AG238" s="3"/>
       <c r="AH238" s="3">
@@ -18320,7 +18314,7 @@
         <v>120000403</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>137</v>
@@ -18332,7 +18326,7 @@
         <v>15</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="I239" s="3">
         <v>1</v>
@@ -18349,10 +18343,10 @@
         <v>100500501</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E240" s="3">
         <v>2</v>
@@ -18361,7 +18355,7 @@
         <v>15</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="I240" s="3">
         <v>1</v>
@@ -18378,22 +18372,22 @@
         <v>101401012</v>
       </c>
       <c r="B241" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="C241" s="17" t="s">
+        <v>781</v>
+      </c>
+      <c r="E241" s="3">
+        <v>3</v>
+      </c>
+      <c r="F241" s="3" t="s">
         <v>782</v>
-      </c>
-      <c r="C241" s="17" t="s">
-        <v>783</v>
-      </c>
-      <c r="E241" s="3">
-        <v>3</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>784</v>
       </c>
       <c r="G241" s="3">
         <v>11</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="I241" s="3">
         <v>3</v>
@@ -18411,16 +18405,16 @@
         <v>0</v>
       </c>
       <c r="U241" s="19" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AD241" s="3">
         <v>26</v>
       </c>
       <c r="AE241" s="17" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AF241" s="10" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AH241" s="3">
         <v>1</v>
@@ -18434,22 +18428,22 @@
         <v>100700401</v>
       </c>
       <c r="B242" s="21" t="s">
+        <v>787</v>
+      </c>
+      <c r="C242" s="18" t="s">
+        <v>788</v>
+      </c>
+      <c r="E242" s="3">
+        <v>3</v>
+      </c>
+      <c r="F242" s="3" t="s">
         <v>789</v>
-      </c>
-      <c r="C242" s="18" t="s">
-        <v>790</v>
-      </c>
-      <c r="E242" s="3">
-        <v>3</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>791</v>
       </c>
       <c r="G242" s="3">
         <v>6</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="I242" s="3">
         <v>3</v>
@@ -18467,10 +18461,10 @@
         <v>10</v>
       </c>
       <c r="AE242" s="21" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AF242" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="AH242" s="3">
         <v>1</v>
@@ -18481,10 +18475,10 @@
         <v>101401013</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E243" s="3">
         <v>2</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_buff.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_buff.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_buff" sheetId="1" r:id="rId1"/>
@@ -4344,7 +4349,7 @@
     <t>畅玩卡倒计时</t>
   </si>
   <si>
-    <t xml:space="preserve"> \n激活后开启以下特权：\n&lt;color=#00FF00&gt;世界聊天\n随身商店\n随身仓库\n自动维修、买药\n自动回收、拾取\n交易行\n面对面交易\n材料解绑\n宝石解绑\n宝石爆率*200%&lt;/color&gt;</t>
+    <t xml:space="preserve"> \n激活后开启以下特权：\n&lt;color=#00FF00&gt;世界聊天\n随身商店\n随身仓库\n自动维修\n自动买药\n交易行&lt;/color&gt;</t>
   </si>
   <si>
     <t>黄金特权卡</t>
@@ -11015,7 +11020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36">
+    <row r="57" ht="14" customHeight="1" spans="1:36">
       <c r="A57" s="3">
         <v>30000013</v>
       </c>
